--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential BSE Midcap Select ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential BSE Midcap Select ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="115">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential BSE Midcap Select ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,6 +70,15 @@
     <t>Healthcare Services</t>
   </si>
   <si>
+    <t>Suzlon Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE040H01021</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
     <t>The Indian Hotels Company Ltd.</t>
   </si>
   <si>
@@ -79,15 +88,6 @@
     <t>Leisure Services</t>
   </si>
   <si>
-    <t>Suzlon Energy Ltd.</t>
-  </si>
-  <si>
-    <t>INE040H01021</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
     <t>Persistent Systems Ltd.</t>
   </si>
   <si>
@@ -106,6 +106,12 @@
     <t>Financial Technology (Fintech)</t>
   </si>
   <si>
+    <t>COFORGE Ltd.</t>
+  </si>
+  <si>
+    <t>INE591G01017</t>
+  </si>
+  <si>
     <t>Dixon Technologies (India) Ltd.</t>
   </si>
   <si>
@@ -115,10 +121,13 @@
     <t>Consumer Durables</t>
   </si>
   <si>
-    <t>COFORGE Ltd.</t>
-  </si>
-  <si>
-    <t>INE591G01017</t>
+    <t>The Federal Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE171A01029</t>
+  </si>
+  <si>
+    <t>Banks</t>
   </si>
   <si>
     <t>Lupin Ltd.</t>
@@ -130,13 +139,13 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>The Federal Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE171A01029</t>
-  </si>
-  <si>
-    <t>Banks</t>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
   </si>
   <si>
     <t>CG Power and Industrial Solutions Ltd.</t>
@@ -145,21 +154,84 @@
     <t>INE067A01029</t>
   </si>
   <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
     <t>IDFC First Bank Ltd.</t>
   </si>
   <si>
     <t>INE092T01019</t>
   </si>
   <si>
+    <t>Yes Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE528G01035</t>
+  </si>
+  <si>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>AU Small Finance Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE949L01017</t>
+  </si>
+  <si>
+    <t>UPL Ltd.</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>Bharat Heavy Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE257A01026</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
+    <t>Bharat Forge Ltd.</t>
+  </si>
+  <si>
+    <t>INE465A01025</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Tube Investments of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE974X01010</t>
+  </si>
+  <si>
+    <t>APL Apollo Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE702C01027</t>
+  </si>
+  <si>
     <t>Colgate - Palmolive (India) Ltd.</t>
   </si>
   <si>
@@ -169,55 +241,31 @@
     <t>Personal Products</t>
   </si>
   <si>
-    <t>Yes Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE528G01035</t>
-  </si>
-  <si>
-    <t>Tube Investments of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE974X01010</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>AU Small Finance Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE949L01017</t>
-  </si>
-  <si>
     <t>Aurobindo Pharma Ltd.</t>
   </si>
   <si>
     <t>INE406A01037</t>
   </si>
   <si>
-    <t>Bharat Forge Ltd.</t>
-  </si>
-  <si>
-    <t>INE465A01025</t>
-  </si>
-  <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+    <t>Godrej Properties Ltd.</t>
+  </si>
+  <si>
+    <t>INE484J01027</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Mphasis Ltd.</t>
+  </si>
+  <si>
+    <t>INE356A01018</t>
   </si>
   <si>
     <t>Voltas Ltd.</t>
@@ -226,34 +274,10 @@
     <t>INE226A01021</t>
   </si>
   <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>APL Apollo Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE702C01027</t>
-  </si>
-  <si>
-    <t>Bharat Heavy Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE257A01026</t>
-  </si>
-  <si>
-    <t>Godrej Properties Ltd.</t>
-  </si>
-  <si>
-    <t>INE484J01027</t>
-  </si>
-  <si>
-    <t>Realty</t>
+    <t>The Phoenix Mills Ltd.</t>
+  </si>
+  <si>
+    <t>INE211B01039</t>
   </si>
   <si>
     <t>Supreme Industries Ltd.</t>
@@ -262,30 +286,6 @@
     <t>INE195A01028</t>
   </si>
   <si>
-    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE335Y01020</t>
-  </si>
-  <si>
-    <t>MRF Ltd.</t>
-  </si>
-  <si>
-    <t>INE883A01011</t>
-  </si>
-  <si>
-    <t>Tata Elxsi Ltd.</t>
-  </si>
-  <si>
-    <t>INE670A01012</t>
-  </si>
-  <si>
-    <t>Astral Ltd.</t>
-  </si>
-  <si>
-    <t>INE006I01046</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -328,6 +328,9 @@
     <t>TREPS</t>
   </si>
   <si>
+    <t>^</t>
+  </si>
+  <si>
     <t>Net Current Assets</t>
   </si>
   <si>
@@ -337,13 +340,16 @@
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -353,9 +359,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - BSE Midcap Select TRI</t>
   </si>
 </sst>
 </file>
@@ -726,13 +729,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -750,8 +753,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="15697200"/>
-          <a:ext cx="3686175" cy="1905000"/>
+          <a:off x="666750" y="15887700"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -765,13 +768,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -789,8 +792,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="18554700"/>
-          <a:ext cx="3686175" cy="1905000"/>
+          <a:off x="666750" y="18745200"/>
+          <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1127,7 +1130,7 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="55.285714285714285" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.285714285714285" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="50.285714285714285" collapsed="true"/>
@@ -1223,10 +1226,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>7898.890000000002</v>
+        <v>8713.8</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9997132067242002</v>
+        <v>0.9993639978139</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1260,10 +1263,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>7898.890000000002</v>
+        <v>8713.8</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9997132067242002</v>
+        <v>0.9993639978139</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1286,13 +1289,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>49388</v>
+        <v>50140</v>
       </c>
       <c r="G8" s="15">
-        <v>524.62</v>
+        <v>564.05</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0663978790073</v>
+        <v>0.0646894882792</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1315,13 +1318,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>58996</v>
+        <v>759481</v>
       </c>
       <c r="G9" s="15">
-        <v>451.02</v>
+        <v>542.73</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0570827863785</v>
+        <v>0.0622443506316</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1344,13 +1347,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>747835</v>
+        <v>59892</v>
       </c>
       <c r="G10" s="15">
-        <v>434.87</v>
+        <v>460.96</v>
       </c>
       <c r="H10" s="16">
-        <v>0.055038781678</v>
+        <v>0.0528663531906</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1373,13 +1376,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>7083</v>
+        <v>7192</v>
       </c>
       <c r="G11" s="15">
-        <v>427.42</v>
+        <v>405.36</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0540958816768</v>
+        <v>0.0464897278058</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1402,13 +1405,13 @@
         <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>21952</v>
+        <v>22440</v>
       </c>
       <c r="G12" s="15">
-        <v>379.08</v>
+        <v>395.10</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0479777895888</v>
+        <v>0.0453130339848</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1428,16 +1431,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F13" s="14">
-        <v>2479</v>
+        <v>4493</v>
       </c>
       <c r="G13" s="15">
-        <v>371.65</v>
+        <v>384.20</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0470374208628</v>
+        <v>0.0440629401593</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1448,25 +1451,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="F14" s="14">
-        <v>4414</v>
+        <v>2610</v>
       </c>
       <c r="G14" s="15">
-        <v>364.81</v>
+        <v>383.45</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0461717247544</v>
+        <v>0.0439769245291</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1489,13 +1492,13 @@
         <v>37</v>
       </c>
       <c r="F15" s="14">
-        <v>16164</v>
+        <v>166572</v>
       </c>
       <c r="G15" s="15">
-        <v>336.34</v>
+        <v>336.48</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0425684545486</v>
+        <v>0.038590052329</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1518,13 +1521,13 @@
         <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>163949</v>
+        <v>16419</v>
       </c>
       <c r="G16" s="15">
-        <v>307.4</v>
+        <v>321.55</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0389056993764</v>
+        <v>0.0368777678507</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1544,16 +1547,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F17" s="14">
-        <v>42919</v>
+        <v>9218</v>
       </c>
       <c r="G17" s="15">
-        <v>272.43</v>
+        <v>301.17</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0344797647401</v>
+        <v>0.0345404364596</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1564,25 +1567,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>9076</v>
+        <v>43576</v>
       </c>
       <c r="G18" s="15">
-        <v>264.72</v>
+        <v>298.95</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0335039581617</v>
+        <v>0.0342858301942</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1602,16 +1605,16 @@
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F19" s="14">
-        <v>411067</v>
+        <v>417359</v>
       </c>
       <c r="G19" s="15">
-        <v>259.96</v>
+        <v>283.93</v>
       </c>
       <c r="H19" s="16">
-        <v>0.032901514671</v>
+        <v>0.0325632238403</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1631,16 +1634,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F20" s="14">
-        <v>8910</v>
+        <v>1276753</v>
       </c>
       <c r="G20" s="15">
-        <v>251.37</v>
+        <v>274.12</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0318143319852</v>
+        <v>0.0314381393974</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1651,25 +1654,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F21" s="14">
-        <v>1257614</v>
+        <v>64984</v>
       </c>
       <c r="G21" s="15">
-        <v>242.09</v>
+        <v>267.18</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0306398203059</v>
+        <v>0.0306422080993</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1689,16 +1692,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="F22" s="14">
-        <v>7109</v>
+        <v>37888</v>
       </c>
       <c r="G22" s="15">
-        <v>236.35</v>
+        <v>262.6</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0299133443318</v>
+        <v>0.0301169393176</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1709,25 +1712,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="F23" s="14">
-        <v>64019</v>
+        <v>39007</v>
       </c>
       <c r="G23" s="15">
-        <v>229.28</v>
+        <v>244.92</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0290185385589</v>
+        <v>0.0280892641952</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1738,25 +1741,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="F24" s="14">
-        <v>37288</v>
+        <v>97696</v>
       </c>
       <c r="G24" s="15">
-        <v>224.23</v>
+        <v>230.56</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0283793915783</v>
+        <v>0.0264423515958</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1776,16 +1779,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>18636</v>
+        <v>87473</v>
       </c>
       <c r="G25" s="15">
-        <v>218.37</v>
+        <v>227.69</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0276377279532</v>
+        <v>0.026113198451</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1805,16 +1808,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F26" s="14">
-        <v>17115</v>
+        <v>7119</v>
       </c>
       <c r="G26" s="15">
-        <v>209.57</v>
+        <v>225.95</v>
       </c>
       <c r="H26" s="16">
-        <v>0.026523966878</v>
+        <v>0.0259136421889</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1837,13 +1840,13 @@
         <v>67</v>
       </c>
       <c r="F27" s="14">
-        <v>96193</v>
+        <v>18192</v>
       </c>
       <c r="G27" s="15">
-        <v>208.64</v>
+        <v>225.83</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0264062625826</v>
+        <v>0.0258998796881</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1863,16 +1866,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F28" s="14">
-        <v>15261</v>
+        <v>7353</v>
       </c>
       <c r="G28" s="15">
-        <v>192.43</v>
+        <v>224.72</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0243546640566</v>
+        <v>0.0257725765554</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1892,16 +1895,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="F29" s="14">
-        <v>5374</v>
+        <v>12242</v>
       </c>
       <c r="G29" s="15">
-        <v>187.15</v>
+        <v>222.13</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0236864074115</v>
+        <v>0.0254755359125</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1912,25 +1915,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="D30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="F30" s="14">
-        <v>12055</v>
+        <v>8860</v>
       </c>
       <c r="G30" s="15">
-        <v>181.96</v>
+        <v>217.52</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0230295415046</v>
+        <v>0.0249468265056</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -1950,16 +1953,16 @@
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F31" s="14">
-        <v>86132</v>
+        <v>18919</v>
       </c>
       <c r="G31" s="15">
-        <v>179.28</v>
+        <v>217.10</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0226903506317</v>
+        <v>0.0248986577527</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -1982,13 +1985,13 @@
         <v>79</v>
       </c>
       <c r="F32" s="14">
-        <v>7621</v>
+        <v>9604</v>
       </c>
       <c r="G32" s="15">
-        <v>177.53</v>
+        <v>215.70</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0224688640543</v>
+        <v>0.024738095243</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2008,16 +2011,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F33" s="14">
-        <v>4326</v>
+        <v>5458</v>
       </c>
       <c r="G33" s="15">
-        <v>171.77</v>
+        <v>209.04</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0217398568051</v>
+        <v>0.0239742764469</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2037,16 +2040,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F34" s="14">
-        <v>20318</v>
+        <v>7732</v>
       </c>
       <c r="G34" s="15">
-        <v>167.01</v>
+        <v>197.90</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0211374133144</v>
+        <v>0.0226966576198</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2066,16 +2069,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F35" s="14">
-        <v>137</v>
+        <v>15519</v>
       </c>
       <c r="G35" s="15">
-        <v>155.64</v>
+        <v>196.14</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0196983833797</v>
+        <v>0.0224948076076</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2095,16 +2098,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="F36" s="14">
-        <v>2330</v>
+        <v>12638</v>
       </c>
       <c r="G36" s="15">
-        <v>147.53</v>
+        <v>194.59</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0186719512979</v>
+        <v>0.0223170419719</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2124,16 +2127,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F37" s="14">
-        <v>8252</v>
+        <v>4388</v>
       </c>
       <c r="G37" s="15">
-        <v>124.37</v>
+        <v>182.18</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0157407346501</v>
+        <v>0.020893770011</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2648,10 +2651,10 @@
         <v>13</v>
       </c>
       <c r="G65" s="9">
-        <v>3.37</v>
-      </c>
-      <c r="H65" s="10">
-        <v>0.0004265198662</v>
+        <v>0.21</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>13</v>
@@ -2670,7 +2673,7 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C67" s="18" t="s">
         <v>13</v>
@@ -2685,10 +2688,10 @@
         <v>13</v>
       </c>
       <c r="G67" s="18">
-        <v>-1.104001600000629</v>
+        <v>5.335522800000035</v>
       </c>
       <c r="H67" s="19">
-        <v>-0.00013972659193467278</v>
+        <v>0.0006119178080566149</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>13</v>
@@ -2699,7 +2702,7 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>13</v>
@@ -2714,10 +2717,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="18">
-        <v>7901.1559984</v>
+        <v>8719.3455228</v>
       </c>
       <c r="H68" s="19">
-        <v>0.9999999999984653</v>
+        <v>0.9999999999983564</v>
       </c>
       <c r="I68" s="18" t="s">
         <v>13</v>
@@ -2728,7 +2731,7 @@
     </row>
     <row r="71" spans="2:9" ht="15" customHeight="1">
       <c r="B71" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
@@ -2740,7 +2743,7 @@
     </row>
     <row r="72" spans="2:8" ht="15" customHeight="1">
       <c r="B72" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
@@ -2749,9 +2752,9 @@
       <c r="G72" s="21"/>
       <c r="H72" s="21"/>
     </row>
-    <row r="73" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B73" s="22" t="s">
-        <v>108</v>
+    <row r="73" spans="2:8" ht="15" customHeight="1">
+      <c r="B73" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
@@ -2762,7 +2765,7 @@
     </row>
     <row r="74" spans="2:8" ht="27.6" customHeight="1">
       <c r="B74" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
@@ -2773,7 +2776,7 @@
     </row>
     <row r="75" spans="2:8" ht="27.6" customHeight="1">
       <c r="B75" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
@@ -2782,26 +2785,33 @@
       <c r="G75" s="21"/>
       <c r="H75" s="21"/>
     </row>
-    <row r="78" ht="15">
-      <c r="B78" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="93" ht="15">
-      <c r="B93" s="21" t="s">
+    <row r="76" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B76" s="22" t="s">
         <v>112</v>
+      </c>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21"/>
+    </row>
+    <row r="79" ht="15">
+      <c r="B79" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="94" ht="15">
       <c r="B94" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B73:H73"/>
     <mergeCell ref="B74:H74"/>
     <mergeCell ref="B75:H75"/>
+    <mergeCell ref="B76:H76"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
